--- a/public/quizzes.xlsx
+++ b/public/quizzes.xlsx
@@ -1,41 +1,170 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\junrelfiles\COA-S.A.F.E\public\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953ACFE7-2C47-4337-817B-42741B811380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Monthly Quizzes" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="46">
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>QuizTitle</t>
+  </si>
+  <si>
+    <t>QuizDescription</t>
+  </si>
+  <si>
+    <t>PassingScore</t>
+  </si>
+  <si>
+    <t>QuestionId</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>Option1</t>
+  </si>
+  <si>
+    <t>Option2</t>
+  </si>
+  <si>
+    <t>Option3</t>
+  </si>
+  <si>
+    <t>Option4</t>
+  </si>
+  <si>
+    <t>CorrectAnswer</t>
+  </si>
+  <si>
+    <t>Explanation</t>
+  </si>
+  <si>
+    <t>Children's Rights Foundation</t>
+  </si>
+  <si>
+    <t>Test your knowledge about basic children's rights and protection</t>
+  </si>
+  <si>
+    <t>What does Article 6 of the UN Convention on the Rights of the Child guarantee?</t>
+  </si>
+  <si>
+    <t>Right to education</t>
+  </si>
+  <si>
+    <t>Right to life and survival</t>
+  </si>
+  <si>
+    <t>Right to play</t>
+  </si>
+  <si>
+    <t>Right to privacy</t>
+  </si>
+  <si>
+    <t>Article 6 guarantees every child's fundamental right to life, survival and development.</t>
+  </si>
+  <si>
+    <t>Article 19 protects children from what?</t>
+  </si>
+  <si>
+    <t>Poverty</t>
+  </si>
+  <si>
+    <t>Illness</t>
+  </si>
+  <si>
+    <t>Violence and abuse</t>
+  </si>
+  <si>
+    <t>Discrimination</t>
+  </si>
+  <si>
+    <t>Article 19 protects children from all forms of physical or mental violence, injury or abuse.</t>
+  </si>
+  <si>
+    <t>What age group does the UN Convention on the Rights of the Child cover?</t>
+  </si>
+  <si>
+    <t>0-16 years old</t>
+  </si>
+  <si>
+    <t>0-18 years old</t>
+  </si>
+  <si>
+    <t>5-18 years old</t>
+  </si>
+  <si>
+    <t>0-21 years old</t>
+  </si>
+  <si>
+    <t>The Convention applies to everyone under 18 years old.</t>
+  </si>
+  <si>
+    <t>Child Participation and Expression</t>
+  </si>
+  <si>
+    <t>Learn about children's rights to be heard and participate in decisions</t>
+  </si>
+  <si>
+    <t>Article 12 ensures children have the right to what?</t>
+  </si>
+  <si>
+    <t>Free healthcare</t>
+  </si>
+  <si>
+    <t>Express their views and be heard</t>
+  </si>
+  <si>
+    <t>Free education</t>
+  </si>
+  <si>
+    <t>Safe housing</t>
+  </si>
+  <si>
+    <t>Article 12 ensures children can express their views freely in all matters affecting them.</t>
+  </si>
+  <si>
+    <t>What does Article 13 guarantee?</t>
+  </si>
+  <si>
+    <t>Freedom of expression and information</t>
+  </si>
+  <si>
+    <t>Freedom from work</t>
+  </si>
+  <si>
+    <t>Freedom from school</t>
+  </si>
+  <si>
+    <t>Freedom to travel</t>
+  </si>
+  <si>
+    <t>Article 13 guarantees children's freedom of expression and the right to seek and receive information.</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +194,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,70 +533,68 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="50.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="60.83203125" customWidth="1"/>
-    <col min="7" max="7" width="25.83203125" customWidth="1"/>
-    <col min="8" max="8" width="25.83203125" customWidth="1"/>
-    <col min="9" max="9" width="25.83203125" customWidth="1"/>
-    <col min="10" max="10" width="25.83203125" customWidth="1"/>
-    <col min="11" max="11" width="15.83203125" customWidth="1"/>
-    <col min="12" max="12" width="60.83203125" customWidth="1"/>
+    <col min="1" max="1" width="8.796875" customWidth="1"/>
+    <col min="2" max="2" width="30.796875" customWidth="1"/>
+    <col min="3" max="3" width="50.796875" customWidth="1"/>
+    <col min="4" max="4" width="12.796875" customWidth="1"/>
+    <col min="5" max="5" width="10.796875" customWidth="1"/>
+    <col min="6" max="6" width="60.796875" customWidth="1"/>
+    <col min="7" max="10" width="25.796875" customWidth="1"/>
+    <col min="11" max="11" width="15.796875" customWidth="1"/>
+    <col min="12" max="12" width="60.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Month</v>
-      </c>
-      <c r="B1" t="str">
-        <v>QuizTitle</v>
-      </c>
-      <c r="C1" t="str">
-        <v>QuizDescription</v>
-      </c>
-      <c r="D1" t="str">
-        <v>PassingScore</v>
-      </c>
-      <c r="E1" t="str">
-        <v>QuestionId</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Question</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Option1</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Option2</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Option3</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Option4</v>
-      </c>
-      <c r="K1" t="str">
-        <v>CorrectAnswer</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Explanation</v>
+    <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>Children's Rights Foundation</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Test your knowledge about basic children's rights and protection</v>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
       </c>
       <c r="D2">
         <v>70</v>
@@ -467,37 +602,37 @@
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2" t="str">
-        <v>What does Article 6 of the UN Convention on the Rights of the Child guarantee?</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Right to education</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Right to life and survival</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Right to play</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Right to privacy</v>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
       </c>
       <c r="K2">
         <v>1</v>
       </c>
-      <c r="L2" t="str">
-        <v>Article 6 guarantees every child's fundamental right to life, survival and development.</v>
+      <c r="L2" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" t="str">
-        <v>Children's Rights Foundation</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Test your knowledge about basic children's rights and protection</v>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
       </c>
       <c r="D3">
         <v>70</v>
@@ -505,37 +640,37 @@
       <c r="E3">
         <v>2</v>
       </c>
-      <c r="F3" t="str">
-        <v>Article 19 protects children from what?</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Poverty</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Illness</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Violence and abuse</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Discrimination</v>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
       </c>
       <c r="K3">
         <v>2</v>
       </c>
-      <c r="L3" t="str">
-        <v>Article 19 protects children from all forms of physical or mental violence, injury or abuse.</v>
+      <c r="L3" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" t="str">
-        <v>Children's Rights Foundation</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Test your knowledge about basic children's rights and protection</v>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
       </c>
       <c r="D4">
         <v>70</v>
@@ -543,37 +678,37 @@
       <c r="E4">
         <v>3</v>
       </c>
-      <c r="F4" t="str">
-        <v>What age group does the UN Convention on the Rights of the Child cover?</v>
-      </c>
-      <c r="G4" t="str">
-        <v>0-16 years old</v>
-      </c>
-      <c r="H4" t="str">
-        <v>0-18 years old</v>
-      </c>
-      <c r="I4" t="str">
-        <v>5-18 years old</v>
-      </c>
-      <c r="J4" t="str">
-        <v>0-21 years old</v>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" t="s">
+        <v>30</v>
       </c>
       <c r="K4">
         <v>1</v>
       </c>
-      <c r="L4" t="str">
-        <v>The Convention applies to everyone under 18 years old.</v>
+      <c r="L4" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" t="str">
-        <v>Child Participation and Expression</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Learn about children's rights to be heard and participate in decisions</v>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
       </c>
       <c r="D5">
         <v>70</v>
@@ -581,37 +716,37 @@
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5" t="str">
-        <v>Article 12 ensures children have the right to what?</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Free healthcare</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Express their views and be heard</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Free education</v>
-      </c>
-      <c r="J5" t="str">
-        <v>Safe housing</v>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" t="s">
+        <v>38</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
-      <c r="L5" t="str">
-        <v>Article 12 ensures children can express their views freely in all matters affecting them.</v>
+      <c r="L5" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2</v>
       </c>
-      <c r="B6" t="str">
-        <v>Child Participation and Expression</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Learn about children's rights to be heard and participate in decisions</v>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
       </c>
       <c r="D6">
         <v>70</v>
@@ -619,31 +754,32 @@
       <c r="E6">
         <v>2</v>
       </c>
-      <c r="F6" t="str">
-        <v>What does Article 13 guarantee?</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Freedom of expression and information</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Freedom from work</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Freedom from school</v>
-      </c>
-      <c r="J6" t="str">
-        <v>Freedom to travel</v>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" t="s">
+        <v>44</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
-      <c r="L6" t="str">
-        <v>Article 13 guarantees children's freedom of expression and the right to seek and receive information.</v>
+      <c r="L6" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError sqref="A1:L6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>